--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,30 @@
         <v>1198.8</v>
       </c>
       <c r="F2" t="n">
+        <v>186.03</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>00:54:05</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>60877</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1778.05</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1198.8</v>
+      </c>
+      <c r="F3" t="n">
         <v>186.03</v>
       </c>
     </row>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,6 +470,30 @@
       </c>
       <c r="F2" t="n">
         <v>183.68</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>00:54:45</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>61230</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1802.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1180.4</v>
+      </c>
+      <c r="F3" t="n">
+        <v>183.14</v>
       </c>
     </row>
   </sheetData>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -494,6 +494,30 @@
       </c>
       <c r="F3" t="n">
         <v>183.14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-14</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>00:56:18</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>61860</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1823.89</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1179.6</v>
+      </c>
+      <c r="F4" t="n">
+        <v>180.25</v>
       </c>
     </row>
   </sheetData>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,30 @@
         <v>1179.6</v>
       </c>
       <c r="F4" t="n">
+        <v>180.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-15</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>00:55:28</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>62090</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1829.32</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1179.6</v>
+      </c>
+      <c r="F5" t="n">
         <v>180.25</v>
       </c>
     </row>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -541,6 +541,30 @@
         <v>1179.6</v>
       </c>
       <c r="F5" t="n">
+        <v>180.25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>00:00:21</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>63704</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1912.05</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1179.6</v>
+      </c>
+      <c r="F6" t="n">
         <v>180.25</v>
       </c>
     </row>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -568,6 +568,30 @@
         <v>180.25</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>00:01:12</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>64979</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2049.27</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1197.4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>183.22</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -592,6 +592,30 @@
         <v>183.22</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>00:05:41</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>64385</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2018.17</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1193.8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>181.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -616,6 +616,30 @@
         <v>181.93</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>00:02:51</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>62062</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1913.65</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1191</v>
+      </c>
+      <c r="F9" t="n">
+        <v>180.4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,54 @@
       </c>
       <c r="N2" t="n">
         <v>54041.88</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>00:01:27</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>60625</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1848.73</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1168.6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G3" t="n">
+        <v>51.62</v>
+      </c>
+      <c r="H3" t="n">
+        <v>109.85</v>
+      </c>
+      <c r="I3" t="n">
+        <v>109.94</v>
+      </c>
+      <c r="J3" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="K3" t="n">
+        <v>154.13</v>
+      </c>
+      <c r="L3" t="n">
+        <v>129021.49</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2011.64</v>
+      </c>
+      <c r="N3" t="n">
+        <v>54536.49</v>
       </c>
     </row>
   </sheetData>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,6 +582,54 @@
       </c>
       <c r="N3" t="n">
         <v>54536.49</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>00:00:41</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>61167</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1862.92</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1128.2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G4" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="H4" t="n">
+        <v>108.77</v>
+      </c>
+      <c r="I4" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="K4" t="n">
+        <v>149.2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>124765.43</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1883.42</v>
+      </c>
+      <c r="N4" t="n">
+        <v>53330.83</v>
       </c>
     </row>
   </sheetData>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -630,6 +630,54 @@
       </c>
       <c r="N4" t="n">
         <v>53330.83</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>00:52:01</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>60064</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1829.9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1128.2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G5" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="H5" t="n">
+        <v>108.77</v>
+      </c>
+      <c r="I5" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="K5" t="n">
+        <v>149.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>127067.98</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1934.92</v>
+      </c>
+      <c r="N5" t="n">
+        <v>54730.7</v>
       </c>
     </row>
   </sheetData>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,6 +678,54 @@
       </c>
       <c r="N5" t="n">
         <v>54730.7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>00:57:22</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>58702</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1775.58</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1128.2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="G6" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="H6" t="n">
+        <v>108.77</v>
+      </c>
+      <c r="I6" t="n">
+        <v>109.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="K6" t="n">
+        <v>149.55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>124700.78</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1908.88</v>
+      </c>
+      <c r="N6" t="n">
+        <v>53330.78</v>
       </c>
     </row>
   </sheetData>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -726,6 +726,54 @@
       </c>
       <c r="N6" t="n">
         <v>53330.78</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>00:04:55</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>60884</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1851.92</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1175.4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="G7" t="n">
+        <v>50.93</v>
+      </c>
+      <c r="H7" t="n">
+        <v>109.18</v>
+      </c>
+      <c r="I7" t="n">
+        <v>109.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="K7" t="n">
+        <v>151.17</v>
+      </c>
+      <c r="L7" t="n">
+        <v>122642.96</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1933.31</v>
+      </c>
+      <c r="N7" t="n">
+        <v>52117.73</v>
       </c>
     </row>
   </sheetData>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,54 @@
       </c>
       <c r="N7" t="n">
         <v>52117.73</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>00:03:31</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>60495</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1845.81</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1201.6</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G8" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="H8" t="n">
+        <v>109.22</v>
+      </c>
+      <c r="I8" t="n">
+        <v>109.24</v>
+      </c>
+      <c r="J8" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="K8" t="n">
+        <v>150.81</v>
+      </c>
+      <c r="L8" t="n">
+        <v>123816.8</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1987.51</v>
+      </c>
+      <c r="N8" t="n">
+        <v>53258.47</v>
       </c>
     </row>
   </sheetData>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,6 +822,54 @@
       </c>
       <c r="N8" t="n">
         <v>53258.47</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-03-26</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>00:52:31</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>61613</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1873.25</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1211.6</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G9" t="n">
+        <v>51.84</v>
+      </c>
+      <c r="H9" t="n">
+        <v>110.15</v>
+      </c>
+      <c r="I9" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="K9" t="n">
+        <v>154.52</v>
+      </c>
+      <c r="L9" t="n">
+        <v>124903.74</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1965.74</v>
+      </c>
+      <c r="N9" t="n">
+        <v>52902.6</v>
       </c>
     </row>
   </sheetData>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -870,6 +870,54 @@
       </c>
       <c r="N9" t="n">
         <v>52902.6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>00:00:25</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>59638</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1788.21</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1165.8</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G10" t="n">
+        <v>51.74</v>
+      </c>
+      <c r="H10" t="n">
+        <v>108.99</v>
+      </c>
+      <c r="I10" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="K10" t="n">
+        <v>148.36</v>
+      </c>
+      <c r="L10" t="n">
+        <v>122669.64</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1922.72</v>
+      </c>
+      <c r="N10" t="n">
+        <v>51404.37</v>
       </c>
     </row>
   </sheetData>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,6 +920,54 @@
         <v>51404.37</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-03-28</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>00:47:03</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>57371</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1723.44</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1165.8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G11" t="n">
+        <v>51.74</v>
+      </c>
+      <c r="H11" t="n">
+        <v>108.99</v>
+      </c>
+      <c r="I11" t="n">
+        <v>108.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="K11" t="n">
+        <v>145.54</v>
+      </c>
+      <c r="L11" t="n">
+        <v>126291.52</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1948.86</v>
+      </c>
+      <c r="N11" t="n">
+        <v>52133.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N11"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -968,6 +968,54 @@
         <v>52133.35</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-03-29</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>00:02:08</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>57761</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1740.7</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1146.4</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G12" t="n">
+        <v>51.72</v>
+      </c>
+      <c r="H12" t="n">
+        <v>107.51</v>
+      </c>
+      <c r="I12" t="n">
+        <v>107.17</v>
+      </c>
+      <c r="J12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>145.23</v>
+      </c>
+      <c r="L12" t="n">
+        <v>125201.58</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1938.37</v>
+      </c>
+      <c r="N12" t="n">
+        <v>52137.59</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:N13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,6 +1016,54 @@
         <v>52137.59</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>18:48:48</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>58192</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1791.96</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1161</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G13" t="n">
+        <v>52.66</v>
+      </c>
+      <c r="H13" t="n">
+        <v>110.36</v>
+      </c>
+      <c r="I13" t="n">
+        <v>109.64</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="K13" t="n">
+        <v>152.73</v>
+      </c>
+      <c r="L13" t="n">
+        <v>130533.05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2011.53</v>
+      </c>
+      <c r="N13" t="n">
+        <v>55210.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1064,6 +1064,54 @@
         <v>55210.96</v>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>00:34:23</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>62541</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1963.46</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1270</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G14" t="n">
+        <v>52.38</v>
+      </c>
+      <c r="H14" t="n">
+        <v>112.98</v>
+      </c>
+      <c r="I14" t="n">
+        <v>112.21</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="K14" t="n">
+        <v>160.83</v>
+      </c>
+      <c r="L14" t="n">
+        <v>130531.89</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2092.17</v>
+      </c>
+      <c r="N14" t="n">
+        <v>56169.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1112,6 +1112,54 @@
         <v>56169.37</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>00:36:06</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>60631</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1877.8</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1270</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G15" t="n">
+        <v>52.38</v>
+      </c>
+      <c r="H15" t="n">
+        <v>112.98</v>
+      </c>
+      <c r="I15" t="n">
+        <v>112.21</v>
+      </c>
+      <c r="J15" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="K15" t="n">
+        <v>161.6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>128647.64</v>
+      </c>
+      <c r="M15" t="n">
+        <v>2007.92</v>
+      </c>
+      <c r="N15" t="n">
+        <v>55111.88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1160,6 +1160,54 @@
         <v>55111.88</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>00:44:24</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>63115</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1992.14</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1270</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G16" t="n">
+        <v>52.38</v>
+      </c>
+      <c r="H16" t="n">
+        <v>112.98</v>
+      </c>
+      <c r="I16" t="n">
+        <v>112.21</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8.94</v>
+      </c>
+      <c r="K16" t="n">
+        <v>160.93</v>
+      </c>
+      <c r="L16" t="n">
+        <v>130422.46</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2072.26</v>
+      </c>
+      <c r="N16" t="n">
+        <v>56903.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1208,6 +1208,54 @@
         <v>56903.87</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>00:47:42</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>62757</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1961.94</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1259.8</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G17" t="n">
+        <v>52.43</v>
+      </c>
+      <c r="H17" t="n">
+        <v>112.94</v>
+      </c>
+      <c r="I17" t="n">
+        <v>112.18</v>
+      </c>
+      <c r="J17" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="K17" t="n">
+        <v>166.56</v>
+      </c>
+      <c r="L17" t="n">
+        <v>132543.27</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2168.09</v>
+      </c>
+      <c r="N17" t="n">
+        <v>57564.95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1256,6 +1256,54 @@
         <v>57564.95</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>00:42:56</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>63744</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2011.95</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1284.2</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G18" t="n">
+        <v>52.33</v>
+      </c>
+      <c r="H18" t="n">
+        <v>114.2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>113.46</v>
+      </c>
+      <c r="J18" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>168.46</v>
+      </c>
+      <c r="L18" t="n">
+        <v>131370.26</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2162.45</v>
+      </c>
+      <c r="N18" t="n">
+        <v>57972.21</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1304,6 +1304,54 @@
         <v>57972.21</v>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>00:41:34</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>63576</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1988.26</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1230</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G19" t="n">
+        <v>52.11</v>
+      </c>
+      <c r="H19" t="n">
+        <v>114.64</v>
+      </c>
+      <c r="I19" t="n">
+        <v>114.22</v>
+      </c>
+      <c r="J19" t="n">
+        <v>8.960000000000001</v>
+      </c>
+      <c r="K19" t="n">
+        <v>168.26</v>
+      </c>
+      <c r="L19" t="n">
+        <v>131275.43</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2149.15</v>
+      </c>
+      <c r="N19" t="n">
+        <v>57181.58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1352,6 +1352,54 @@
         <v>57181.58</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>00:40:44</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>65767</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2072.97</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1222.6</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G20" t="n">
+        <v>52.38</v>
+      </c>
+      <c r="H20" t="n">
+        <v>115.32</v>
+      </c>
+      <c r="I20" t="n">
+        <v>115.13</v>
+      </c>
+      <c r="J20" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="K20" t="n">
+        <v>171.39</v>
+      </c>
+      <c r="L20" t="n">
+        <v>132493.87</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2211.15</v>
+      </c>
+      <c r="N20" t="n">
+        <v>57769.01</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1400,6 +1400,54 @@
         <v>57769.01</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>00:36:59</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>64398</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2002.03</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1244</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G21" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="H21" t="n">
+        <v>116.68</v>
+      </c>
+      <c r="I21" t="n">
+        <v>116.45</v>
+      </c>
+      <c r="J21" t="n">
+        <v>9.26</v>
+      </c>
+      <c r="K21" t="n">
+        <v>171.39</v>
+      </c>
+      <c r="L21" t="n">
+        <v>132717.92</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2233.22</v>
+      </c>
+      <c r="N21" t="n">
+        <v>58044.96</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1448,6 +1448,54 @@
         <v>58044.96</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>00:37:32</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>63104</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1932.8</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1244</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G22" t="n">
+        <v>52.26</v>
+      </c>
+      <c r="H22" t="n">
+        <v>116.68</v>
+      </c>
+      <c r="I22" t="n">
+        <v>116.45</v>
+      </c>
+      <c r="J22" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="K22" t="n">
+        <v>171.79</v>
+      </c>
+      <c r="L22" t="n">
+        <v>131608.93</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2183.76</v>
+      </c>
+      <c r="N22" t="n">
+        <v>58652.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1496,6 +1496,54 @@
         <v>58652.61</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>00:39:04</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>64249</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1965.14</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1245</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G23" t="n">
+        <v>52.46</v>
+      </c>
+      <c r="H23" t="n">
+        <v>116.21</v>
+      </c>
+      <c r="I23" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K23" t="n">
+        <v>170.2</v>
+      </c>
+      <c r="L23" t="n">
+        <v>129618.85</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2103.87</v>
+      </c>
+      <c r="N23" t="n">
+        <v>55908</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N23"/>
+  <dimension ref="A1:N24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1544,6 +1544,54 @@
         <v>55908</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>00:50:11</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>67059</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2046.26</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1237</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="G24" t="n">
+        <v>52.18</v>
+      </c>
+      <c r="H24" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>116.26</v>
+      </c>
+      <c r="J24" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="K24" t="n">
+        <v>172.91</v>
+      </c>
+      <c r="L24" t="n">
+        <v>130352.08</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2128.47</v>
+      </c>
+      <c r="N24" t="n">
+        <v>57191.18</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N24"/>
+  <dimension ref="A1:N25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1592,6 +1592,54 @@
         <v>57191.18</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>00:47:44</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>67025</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1999.91</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1249.8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="G25" t="n">
+        <v>52</v>
+      </c>
+      <c r="H25" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="I25" t="n">
+        <v>117.07</v>
+      </c>
+      <c r="J25" t="n">
+        <v>9.289999999999999</v>
+      </c>
+      <c r="K25" t="n">
+        <v>170.79</v>
+      </c>
+      <c r="L25" t="n">
+        <v>129551.14</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2079.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>55463.76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1640,6 +1640,54 @@
         <v>55463.76</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>00:40:25</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>66090</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1971.8</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1221.1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="G26" t="n">
+        <v>52.42</v>
+      </c>
+      <c r="H26" t="n">
+        <v>116.99</v>
+      </c>
+      <c r="I26" t="n">
+        <v>117.6</v>
+      </c>
+      <c r="J26" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K26" t="n">
+        <v>177.61</v>
+      </c>
+      <c r="L26" t="n">
+        <v>129561.75</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2075.14</v>
+      </c>
+      <c r="N26" t="n">
+        <v>55412.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1688,6 +1688,54 @@
         <v>55412.09</v>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>00:38:32</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>66221</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1978.73</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1249.6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G27" t="n">
+        <v>52.34</v>
+      </c>
+      <c r="H27" t="n">
+        <v>116.73</v>
+      </c>
+      <c r="I27" t="n">
+        <v>117.56</v>
+      </c>
+      <c r="J27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="K27" t="n">
+        <v>177.61</v>
+      </c>
+      <c r="L27" t="n">
+        <v>129476.75</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2094.28</v>
+      </c>
+      <c r="N27" t="n">
+        <v>55247.58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1736,6 +1736,54 @@
         <v>55247.58</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>00:40:03</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>66781</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2014.55</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1249.6</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G28" t="n">
+        <v>52.34</v>
+      </c>
+      <c r="H28" t="n">
+        <v>116.73</v>
+      </c>
+      <c r="I28" t="n">
+        <v>117.56</v>
+      </c>
+      <c r="J28" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="K28" t="n">
+        <v>177.82</v>
+      </c>
+      <c r="L28" t="n">
+        <v>129049.39</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2062.89</v>
+      </c>
+      <c r="N28" t="n">
+        <v>55070.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1784,6 +1784,54 @@
         <v>55070.81</v>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>00:53:50</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>65702</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1956.83</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1249.6</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G29" t="n">
+        <v>52.34</v>
+      </c>
+      <c r="H29" t="n">
+        <v>116.73</v>
+      </c>
+      <c r="I29" t="n">
+        <v>117.56</v>
+      </c>
+      <c r="J29" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="K29" t="n">
+        <v>184.73</v>
+      </c>
+      <c r="L29" t="n">
+        <v>128903.72</v>
+      </c>
+      <c r="M29" t="n">
+        <v>2079.8</v>
+      </c>
+      <c r="N29" t="n">
+        <v>54828.09</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1832,6 +1832,54 @@
         <v>54828.09</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>00:57:31</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>65056</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1950.69</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1212.6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G30" t="n">
+        <v>52.12</v>
+      </c>
+      <c r="H30" t="n">
+        <v>116.61</v>
+      </c>
+      <c r="I30" t="n">
+        <v>117.49</v>
+      </c>
+      <c r="J30" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="K30" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="L30" t="n">
+        <v>126427.91</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2020.12</v>
+      </c>
+      <c r="N30" t="n">
+        <v>53502.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1880,6 +1880,54 @@
         <v>53502.24</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>00:58:11</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>65024</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1932.71</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1171.8</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G31" t="n">
+        <v>52.38</v>
+      </c>
+      <c r="H31" t="n">
+        <v>116.26</v>
+      </c>
+      <c r="I31" t="n">
+        <v>117.18</v>
+      </c>
+      <c r="J31" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="K31" t="n">
+        <v>179.14</v>
+      </c>
+      <c r="L31" t="n">
+        <v>125565.65</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1982.85</v>
+      </c>
+      <c r="N31" t="n">
+        <v>51938.27</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1928,6 +1928,54 @@
         <v>51938.27</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>00:54:26</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>65044</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1922.53</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1192.6</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="G32" t="n">
+        <v>51.97</v>
+      </c>
+      <c r="H32" t="n">
+        <v>116.31</v>
+      </c>
+      <c r="I32" t="n">
+        <v>117.53</v>
+      </c>
+      <c r="J32" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="K32" t="n">
+        <v>170.07</v>
+      </c>
+      <c r="L32" t="n">
+        <v>127254.03</v>
+      </c>
+      <c r="M32" t="n">
+        <v>2046.15</v>
+      </c>
+      <c r="N32" t="n">
+        <v>54890.89</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1976,6 +1976,54 @@
         <v>54890.89</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>00:52:01</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>66641</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1953.87</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1222.4</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G33" t="n">
+        <v>52.71</v>
+      </c>
+      <c r="H33" t="n">
+        <v>117.06</v>
+      </c>
+      <c r="I33" t="n">
+        <v>117.74</v>
+      </c>
+      <c r="J33" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="K33" t="n">
+        <v>169.28</v>
+      </c>
+      <c r="L33" t="n">
+        <v>126855.17</v>
+      </c>
+      <c r="M33" t="n">
+        <v>2079.88</v>
+      </c>
+      <c r="N33" t="n">
+        <v>54868.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2024,6 +2024,54 @@
         <v>54868.37</v>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-05-03</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>00:43:11</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>67082</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1979.87</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1222.4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G34" t="n">
+        <v>52.71</v>
+      </c>
+      <c r="H34" t="n">
+        <v>117.06</v>
+      </c>
+      <c r="I34" t="n">
+        <v>117.74</v>
+      </c>
+      <c r="J34" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="K34" t="n">
+        <v>169.28</v>
+      </c>
+      <c r="L34" t="n">
+        <v>126973.09</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2082.92</v>
+      </c>
+      <c r="N34" t="n">
+        <v>54755.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:N35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2072,6 +2072,54 @@
         <v>54755.93</v>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>00:42:52</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>67466</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1995.31</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1222.4</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G35" t="n">
+        <v>52.71</v>
+      </c>
+      <c r="H35" t="n">
+        <v>117.06</v>
+      </c>
+      <c r="I35" t="n">
+        <v>117.74</v>
+      </c>
+      <c r="J35" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="K35" t="n">
+        <v>169</v>
+      </c>
+      <c r="L35" t="n">
+        <v>126844.09</v>
+      </c>
+      <c r="M35" t="n">
+        <v>2085.37</v>
+      </c>
+      <c r="N35" t="n">
+        <v>55164.37</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N35"/>
+  <dimension ref="A1:N36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2120,6 +2120,54 @@
         <v>55164.37</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>00:57:46</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>68500</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2014.21</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1187.4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G36" t="n">
+        <v>52.23</v>
+      </c>
+      <c r="H36" t="n">
+        <v>117.36</v>
+      </c>
+      <c r="I36" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="J36" t="n">
+        <v>9.109999999999999</v>
+      </c>
+      <c r="K36" t="n">
+        <v>169.74</v>
+      </c>
+      <c r="L36" t="n">
+        <v>124498.8</v>
+      </c>
+      <c r="M36" t="n">
+        <v>2011.97</v>
+      </c>
+      <c r="N36" t="n">
+        <v>53827.58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2168,6 +2168,54 @@
         <v>53827.58</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>00:56:55</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>69381</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2025.33</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1187.4</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G37" t="n">
+        <v>52.23</v>
+      </c>
+      <c r="H37" t="n">
+        <v>117.36</v>
+      </c>
+      <c r="I37" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="J37" t="n">
+        <v>9.15</v>
+      </c>
+      <c r="K37" t="n">
+        <v>167.77</v>
+      </c>
+      <c r="L37" t="n">
+        <v>125113.01</v>
+      </c>
+      <c r="M37" t="n">
+        <v>2008.4</v>
+      </c>
+      <c r="N37" t="n">
+        <v>53945.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2216,6 +2216,54 @@
         <v>53945.34</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>00:54:06</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>69202</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1997.43</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1229</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>52.34</v>
+      </c>
+      <c r="H38" t="n">
+        <v>118.21</v>
+      </c>
+      <c r="I38" t="n">
+        <v>119.42</v>
+      </c>
+      <c r="J38" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="K38" t="n">
+        <v>176.82</v>
+      </c>
+      <c r="L38" t="n">
+        <v>128773.75</v>
+      </c>
+      <c r="M38" t="n">
+        <v>2132.51</v>
+      </c>
+      <c r="N38" t="n">
+        <v>56827.63</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N38"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2264,6 +2264,54 @@
         <v>56827.63</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>00:56:02</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>68075</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1959.61</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1300</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G39" t="n">
+        <v>52.04</v>
+      </c>
+      <c r="H39" t="n">
+        <v>140.2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>120.81</v>
+      </c>
+      <c r="J39" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="K39" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="L39" t="n">
+        <v>128816.55</v>
+      </c>
+      <c r="M39" t="n">
+        <v>2204.39</v>
+      </c>
+      <c r="N39" t="n">
+        <v>56430.36</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:N40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2312,6 +2312,54 @@
         <v>56430.36</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>00:46:33</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>68543</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1978.57</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1319.4</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G40" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="H40" t="n">
+        <v>119.51</v>
+      </c>
+      <c r="I40" t="n">
+        <v>121.03</v>
+      </c>
+      <c r="J40" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="K40" t="n">
+        <v>182.53</v>
+      </c>
+      <c r="L40" t="n">
+        <v>128726.55</v>
+      </c>
+      <c r="M40" t="n">
+        <v>2192.39</v>
+      </c>
+      <c r="N40" t="n">
+        <v>55827.68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2360,6 +2360,54 @@
         <v>55827.68</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>00:50:31</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>69630</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2015.1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1319.4</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G41" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="H41" t="n">
+        <v>119.51</v>
+      </c>
+      <c r="I41" t="n">
+        <v>121.03</v>
+      </c>
+      <c r="J41" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="K41" t="n">
+        <v>182.88</v>
+      </c>
+      <c r="L41" t="n">
+        <v>128349.18</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2190.79</v>
+      </c>
+      <c r="N41" t="n">
+        <v>55889.28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N41"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2408,6 +2408,54 @@
         <v>55889.28</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>00:55:35</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>69448</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1987.27</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1319.4</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G42" t="n">
+        <v>51.83</v>
+      </c>
+      <c r="H42" t="n">
+        <v>119.51</v>
+      </c>
+      <c r="I42" t="n">
+        <v>121.03</v>
+      </c>
+      <c r="J42" t="n">
+        <v>9.16</v>
+      </c>
+      <c r="K42" t="n">
+        <v>186.13</v>
+      </c>
+      <c r="L42" t="n">
+        <v>129637.37</v>
+      </c>
+      <c r="M42" t="n">
+        <v>2387.1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>59023.75</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N42"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +2456,54 @@
         <v>59023.75</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>00:57:41</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>69780</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1969.02</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1327</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G43" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="H43" t="n">
+        <v>120.43</v>
+      </c>
+      <c r="I43" t="n">
+        <v>122.05</v>
+      </c>
+      <c r="J43" t="n">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="K43" t="n">
+        <v>201.93</v>
+      </c>
+      <c r="L43" t="n">
+        <v>128481.14</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2322.61</v>
+      </c>
+      <c r="N43" t="n">
+        <v>57215.03</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N43"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2504,6 +2504,54 @@
         <v>57215.03</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-05-16</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>00:55:22</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>68020</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1912.15</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1367</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G44" t="n">
+        <v>52.49</v>
+      </c>
+      <c r="H44" t="n">
+        <v>121.99</v>
+      </c>
+      <c r="I44" t="n">
+        <v>123.94</v>
+      </c>
+      <c r="J44" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="K44" t="n">
+        <v>193.73</v>
+      </c>
+      <c r="L44" t="n">
+        <v>125599.69</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2109.04</v>
+      </c>
+      <c r="N44" t="n">
+        <v>54877.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2552,6 +2552,54 @@
         <v>54877.3</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>00:54:47</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>66993</v>
+      </c>
+      <c r="D45" t="n">
+        <v>1872.6</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1306.6</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="G45" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="H45" t="n">
+        <v>121</v>
+      </c>
+      <c r="I45" t="n">
+        <v>123.33</v>
+      </c>
+      <c r="J45" t="n">
+        <v>8.890000000000001</v>
+      </c>
+      <c r="K45" t="n">
+        <v>193.8</v>
+      </c>
+      <c r="L45" t="n">
+        <v>125953.22</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2131.76</v>
+      </c>
+      <c r="N45" t="n">
+        <v>55272.53</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2600,6 +2600,54 @@
         <v>55272.53</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>00:54:43</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>65905</v>
+      </c>
+      <c r="D46" t="n">
+        <v>1821.57</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1409</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G46" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="H46" t="n">
+        <v>122.83</v>
+      </c>
+      <c r="I46" t="n">
+        <v>124.61</v>
+      </c>
+      <c r="J46" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="K46" t="n">
+        <v>185.55</v>
+      </c>
+      <c r="L46" t="n">
+        <v>125251.13</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2102.56</v>
+      </c>
+      <c r="N46" t="n">
+        <v>53513.62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N46"/>
+  <dimension ref="A1:N47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2648,6 +2648,54 @@
         <v>53513.62</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>00:58:44</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>65912</v>
+      </c>
+      <c r="D47" t="n">
+        <v>1794.87</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1409</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="G47" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="H47" t="n">
+        <v>122.83</v>
+      </c>
+      <c r="I47" t="n">
+        <v>124.61</v>
+      </c>
+      <c r="J47" t="n">
+        <v>8.77</v>
+      </c>
+      <c r="K47" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="L47" t="n">
+        <v>124875.81</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2103.69</v>
+      </c>
+      <c r="N47" t="n">
+        <v>53550.93</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2696,6 +2696,54 @@
         <v>53550.93</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>00:58:20</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>63231</v>
+      </c>
+      <c r="D48" t="n">
+        <v>1731.82</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1384.8</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G48" t="n">
+        <v>52.36</v>
+      </c>
+      <c r="H48" t="n">
+        <v>123.38</v>
+      </c>
+      <c r="I48" t="n">
+        <v>125.32</v>
+      </c>
+      <c r="J48" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="K48" t="n">
+        <v>181.09</v>
+      </c>
+      <c r="L48" t="n">
+        <v>125758.96</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2085.16</v>
+      </c>
+      <c r="N48" t="n">
+        <v>53006</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2744,6 +2744,54 @@
         <v>53006</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>00:58:57</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>55127</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1486.75</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1676</v>
+      </c>
+      <c r="F49" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G49" t="n">
+        <v>51.76</v>
+      </c>
+      <c r="H49" t="n">
+        <v>124.62</v>
+      </c>
+      <c r="I49" t="n">
+        <v>125.81</v>
+      </c>
+      <c r="J49" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="K49" t="n">
+        <v>183.7</v>
+      </c>
+      <c r="L49" t="n">
+        <v>116975.72</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1819.57</v>
+      </c>
+      <c r="N49" t="n">
+        <v>46763.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:N50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2792,6 +2792,54 @@
         <v>46763.38</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>00:58:52</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>52767</v>
+      </c>
+      <c r="D50" t="n">
+        <v>1410.7</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1578.2</v>
+      </c>
+      <c r="F50" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G50" t="n">
+        <v>52.01</v>
+      </c>
+      <c r="H50" t="n">
+        <v>123.73</v>
+      </c>
+      <c r="I50" t="n">
+        <v>124.86</v>
+      </c>
+      <c r="J50" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="K50" t="n">
+        <v>170.6</v>
+      </c>
+      <c r="L50" t="n">
+        <v>113304.05</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1651.76</v>
+      </c>
+      <c r="N50" t="n">
+        <v>44819.74</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N50"/>
+  <dimension ref="A1:N51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2840,6 +2840,54 @@
         <v>44819.74</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>00:57:56</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>55194</v>
+      </c>
+      <c r="D51" t="n">
+        <v>1558.22</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1634.4</v>
+      </c>
+      <c r="F51" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="G51" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="H51" t="n">
+        <v>125.74</v>
+      </c>
+      <c r="I51" t="n">
+        <v>126.64</v>
+      </c>
+      <c r="J51" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="K51" t="n">
+        <v>170.3</v>
+      </c>
+      <c r="L51" t="n">
+        <v>117675.56</v>
+      </c>
+      <c r="M51" t="n">
+        <v>1765.29</v>
+      </c>
+      <c r="N51" t="n">
+        <v>46423.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N51"/>
+  <dimension ref="A1:N52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2888,6 +2888,54 @@
         <v>46423.3</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>00:59:21</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>56109</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1571.31</v>
+      </c>
+      <c r="E52" t="n">
+        <v>1602.8</v>
+      </c>
+      <c r="F52" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="G52" t="n">
+        <v>52.8</v>
+      </c>
+      <c r="H52" t="n">
+        <v>125.72</v>
+      </c>
+      <c r="I52" t="n">
+        <v>127.1</v>
+      </c>
+      <c r="J52" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="K52" t="n">
+        <v>184.74</v>
+      </c>
+      <c r="L52" t="n">
+        <v>116246.74</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1697.71</v>
+      </c>
+      <c r="N52" t="n">
+        <v>46133.81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N52"/>
+  <dimension ref="A1:N53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2936,6 +2936,54 @@
         <v>46133.81</v>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>00:49:25</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>56204</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1588.63</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1569</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G53" t="n">
+        <v>53.03</v>
+      </c>
+      <c r="H53" t="n">
+        <v>126.15</v>
+      </c>
+      <c r="I53" t="n">
+        <v>127.57</v>
+      </c>
+      <c r="J53" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="K53" t="n">
+        <v>184.74</v>
+      </c>
+      <c r="L53" t="n">
+        <v>115548.51</v>
+      </c>
+      <c r="M53" t="n">
+        <v>1683.89</v>
+      </c>
+      <c r="N53" t="n">
+        <v>45556.65</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N53"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2984,6 +2984,54 @@
         <v>45556.65</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>00:49:57</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>55915</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1578.73</v>
+      </c>
+      <c r="E54" t="n">
+        <v>1569</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G54" t="n">
+        <v>53.03</v>
+      </c>
+      <c r="H54" t="n">
+        <v>126.15</v>
+      </c>
+      <c r="I54" t="n">
+        <v>127.57</v>
+      </c>
+      <c r="J54" t="n">
+        <v>9.76</v>
+      </c>
+      <c r="K54" t="n">
+        <v>185.08</v>
+      </c>
+      <c r="L54" t="n">
+        <v>115353.47</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1668.38</v>
+      </c>
+      <c r="N54" t="n">
+        <v>45580.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3032,6 +3032,54 @@
         <v>45580.66</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>00:56:12</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>54393</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1543.5</v>
+      </c>
+      <c r="E55" t="n">
+        <v>1569</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G55" t="n">
+        <v>53.03</v>
+      </c>
+      <c r="H55" t="n">
+        <v>126.15</v>
+      </c>
+      <c r="I55" t="n">
+        <v>127.57</v>
+      </c>
+      <c r="J55" t="n">
+        <v>9.65</v>
+      </c>
+      <c r="K55" t="n">
+        <v>178.76</v>
+      </c>
+      <c r="L55" t="n">
+        <v>113256.97</v>
+      </c>
+      <c r="M55" t="n">
+        <v>1637.38</v>
+      </c>
+      <c r="N55" t="n">
+        <v>45610.02</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:N56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3080,6 +3080,54 @@
         <v>45610.02</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>00:57:00</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>56803</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1648.75</v>
+      </c>
+      <c r="E56" t="n">
+        <v>1540.8</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="G56" t="n">
+        <v>53.34</v>
+      </c>
+      <c r="H56" t="n">
+        <v>126.33</v>
+      </c>
+      <c r="I56" t="n">
+        <v>127.83</v>
+      </c>
+      <c r="J56" t="n">
+        <v>9.789999999999999</v>
+      </c>
+      <c r="K56" t="n">
+        <v>185.41</v>
+      </c>
+      <c r="L56" t="n">
+        <v>114112.94</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1659.84</v>
+      </c>
+      <c r="N56" t="n">
+        <v>46115.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N56"/>
+  <dimension ref="A1:N57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,6 +3128,54 @@
         <v>46115.19</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>00:58:11</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>56540</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1675.61</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1555.8</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G57" t="n">
+        <v>53.51</v>
+      </c>
+      <c r="H57" t="n">
+        <v>126.09</v>
+      </c>
+      <c r="I57" t="n">
+        <v>127.33</v>
+      </c>
+      <c r="J57" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="K57" t="n">
+        <v>185.28</v>
+      </c>
+      <c r="L57" t="n">
+        <v>113970.67</v>
+      </c>
+      <c r="M57" t="n">
+        <v>1628.95</v>
+      </c>
+      <c r="N57" t="n">
+        <v>47335.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N57"/>
+  <dimension ref="A1:N58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3176,6 +3176,54 @@
         <v>47335.24</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>00:56:43</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>55868</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1632.74</v>
+      </c>
+      <c r="E58" t="n">
+        <v>1549.4</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="G58" t="n">
+        <v>53.56</v>
+      </c>
+      <c r="H58" t="n">
+        <v>126.29</v>
+      </c>
+      <c r="I58" t="n">
+        <v>127.61</v>
+      </c>
+      <c r="J58" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="K58" t="n">
+        <v>181.21</v>
+      </c>
+      <c r="L58" t="n">
+        <v>111728.41</v>
+      </c>
+      <c r="M58" t="n">
+        <v>1565.18</v>
+      </c>
+      <c r="N58" t="n">
+        <v>45702.61</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N58"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3224,6 +3224,54 @@
         <v>45702.61</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-07-18</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>00:51:31</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>55875</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1606.25</v>
+      </c>
+      <c r="E59" t="n">
+        <v>1598.4</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G59" t="n">
+        <v>53.92</v>
+      </c>
+      <c r="H59" t="n">
+        <v>126.26</v>
+      </c>
+      <c r="I59" t="n">
+        <v>127.68</v>
+      </c>
+      <c r="J59" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K59" t="n">
+        <v>177.2</v>
+      </c>
+      <c r="L59" t="n">
+        <v>113006.5</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1579.23</v>
+      </c>
+      <c r="N59" t="n">
+        <v>45042.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:N60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3272,6 +3272,54 @@
         <v>45042.49</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>00:51:16</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>56585</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1627.11</v>
+      </c>
+      <c r="E60" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G60" t="n">
+        <v>54.07</v>
+      </c>
+      <c r="H60" t="n">
+        <v>124.85</v>
+      </c>
+      <c r="I60" t="n">
+        <v>126.14</v>
+      </c>
+      <c r="J60" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K60" t="n">
+        <v>177.2</v>
+      </c>
+      <c r="L60" t="n">
+        <v>112717.18</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1574.11</v>
+      </c>
+      <c r="N60" t="n">
+        <v>45107.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3320,6 +3320,54 @@
         <v>45107.1</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>00:53:07</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>56579</v>
+      </c>
+      <c r="D61" t="n">
+        <v>1635.39</v>
+      </c>
+      <c r="E61" t="n">
+        <v>1537</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G61" t="n">
+        <v>54.07</v>
+      </c>
+      <c r="H61" t="n">
+        <v>124.85</v>
+      </c>
+      <c r="I61" t="n">
+        <v>126.14</v>
+      </c>
+      <c r="J61" t="n">
+        <v>9.82</v>
+      </c>
+      <c r="K61" t="n">
+        <v>177.44</v>
+      </c>
+      <c r="L61" t="n">
+        <v>112548.5</v>
+      </c>
+      <c r="M61" t="n">
+        <v>1578.58</v>
+      </c>
+      <c r="N61" t="n">
+        <v>44913.07</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:N62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3368,6 +3368,54 @@
         <v>44913.07</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>00:57:23</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>58121</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1683.17</v>
+      </c>
+      <c r="E62" t="n">
+        <v>1520.8</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G62" t="n">
+        <v>53.94</v>
+      </c>
+      <c r="H62" t="n">
+        <v>125.26</v>
+      </c>
+      <c r="I62" t="n">
+        <v>126.62</v>
+      </c>
+      <c r="J62" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="K62" t="n">
+        <v>181.79</v>
+      </c>
+      <c r="L62" t="n">
+        <v>115195.59</v>
+      </c>
+      <c r="M62" t="n">
+        <v>1667.38</v>
+      </c>
+      <c r="N62" t="n">
+        <v>46210.76</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N62"/>
+  <dimension ref="A1:N63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3416,6 +3416,54 @@
         <v>46210.76</v>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>00:57:18</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>57217</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1653.38</v>
+      </c>
+      <c r="E63" t="n">
+        <v>1589.6</v>
+      </c>
+      <c r="F63" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G63" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="H63" t="n">
+        <v>126.03</v>
+      </c>
+      <c r="I63" t="n">
+        <v>127.2</v>
+      </c>
+      <c r="J63" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="K63" t="n">
+        <v>183.4</v>
+      </c>
+      <c r="L63" t="n">
+        <v>114440.78</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1635.63</v>
+      </c>
+      <c r="N63" t="n">
+        <v>45374.68</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N63"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3464,6 +3464,54 @@
         <v>45374.68</v>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>00:55:56</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>56578</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1648.73</v>
+      </c>
+      <c r="E64" t="n">
+        <v>1563</v>
+      </c>
+      <c r="F64" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G64" t="n">
+        <v>54.49</v>
+      </c>
+      <c r="H64" t="n">
+        <v>125.26</v>
+      </c>
+      <c r="I64" t="n">
+        <v>126.33</v>
+      </c>
+      <c r="J64" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="K64" t="n">
+        <v>183.52</v>
+      </c>
+      <c r="L64" t="n">
+        <v>114965.52</v>
+      </c>
+      <c r="M64" t="n">
+        <v>1657.84</v>
+      </c>
+      <c r="N64" t="n">
+        <v>45035.42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:N65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3512,6 +3512,54 @@
         <v>45035.42</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>00:58:50</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>57365</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1710.21</v>
+      </c>
+      <c r="E65" t="n">
+        <v>1561.12</v>
+      </c>
+      <c r="F65" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>54.49</v>
+      </c>
+      <c r="H65" t="n">
+        <v>125.26</v>
+      </c>
+      <c r="I65" t="n">
+        <v>126.33</v>
+      </c>
+      <c r="J65" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="K65" t="n">
+        <v>181.56</v>
+      </c>
+      <c r="L65" t="n">
+        <v>115597.01</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1697.41</v>
+      </c>
+      <c r="N65" t="n">
+        <v>45894.49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:N66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3560,6 +3560,54 @@
         <v>45894.49</v>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>00:59:36</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>56014</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1678.7</v>
+      </c>
+      <c r="E66" t="n">
+        <v>1429.8</v>
+      </c>
+      <c r="F66" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G66" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="H66" t="n">
+        <v>124.75</v>
+      </c>
+      <c r="I66" t="n">
+        <v>125.56</v>
+      </c>
+      <c r="J66" t="n">
+        <v>9.720000000000001</v>
+      </c>
+      <c r="K66" t="n">
+        <v>172.99</v>
+      </c>
+      <c r="L66" t="n">
+        <v>113375.16</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1613.29</v>
+      </c>
+      <c r="N66" t="n">
+        <v>45399.19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N66"/>
+  <dimension ref="A1:N67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3608,6 +3608,54 @@
         <v>45399.19</v>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>00:58:57</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>55676</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1660.57</v>
+      </c>
+      <c r="E67" t="n">
+        <v>1388.4</v>
+      </c>
+      <c r="F67" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="H67" t="n">
+        <v>125.18</v>
+      </c>
+      <c r="I67" t="n">
+        <v>126.07</v>
+      </c>
+      <c r="J67" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K67" t="n">
+        <v>165.59</v>
+      </c>
+      <c r="L67" t="n">
+        <v>116028.24</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1637.73</v>
+      </c>
+      <c r="N67" t="n">
+        <v>45660.38</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N67"/>
+  <dimension ref="A1:N68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3656,6 +3656,54 @@
         <v>45660.38</v>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>00:56:08</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>54427</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1600.39</v>
+      </c>
+      <c r="E68" t="n">
+        <v>1434.2</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G68" t="n">
+        <v>55.07</v>
+      </c>
+      <c r="H68" t="n">
+        <v>124.23</v>
+      </c>
+      <c r="I68" t="n">
+        <v>124.82</v>
+      </c>
+      <c r="J68" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="K68" t="n">
+        <v>174.15</v>
+      </c>
+      <c r="L68" t="n">
+        <v>112932.53</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1606.26</v>
+      </c>
+      <c r="N68" t="n">
+        <v>46028.14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N68"/>
+  <dimension ref="A1:N69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3704,6 +3704,54 @@
         <v>46028.14</v>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>00:56:58</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>54870</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1627.78</v>
+      </c>
+      <c r="E69" t="n">
+        <v>1440</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="G69" t="n">
+        <v>55.07</v>
+      </c>
+      <c r="H69" t="n">
+        <v>124.23</v>
+      </c>
+      <c r="I69" t="n">
+        <v>124.82</v>
+      </c>
+      <c r="J69" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="K69" t="n">
+        <v>173.77</v>
+      </c>
+      <c r="L69" t="n">
+        <v>114711.18</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1631.79</v>
+      </c>
+      <c r="N69" t="n">
+        <v>46520.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N69"/>
+  <dimension ref="A1:N70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3752,6 +3752,54 @@
         <v>46520.1</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>00:59:24</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>55893</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1649.42</v>
+      </c>
+      <c r="E70" t="n">
+        <v>1472.6</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G70" t="n">
+        <v>55.21</v>
+      </c>
+      <c r="H70" t="n">
+        <v>127.8</v>
+      </c>
+      <c r="I70" t="n">
+        <v>129.13</v>
+      </c>
+      <c r="J70" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="K70" t="n">
+        <v>189.67</v>
+      </c>
+      <c r="L70" t="n">
+        <v>119820.98</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1732.01</v>
+      </c>
+      <c r="N70" t="n">
+        <v>48665.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3800,6 +3800,54 @@
         <v>48665.54</v>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>00:35:34</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>56101</v>
+      </c>
+      <c r="D71" t="n">
+        <v>1655.4</v>
+      </c>
+      <c r="E71" t="n">
+        <v>1494</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G71" t="n">
+        <v>55.14</v>
+      </c>
+      <c r="H71" t="n">
+        <v>128.12</v>
+      </c>
+      <c r="I71" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="J71" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="K71" t="n">
+        <v>193.7</v>
+      </c>
+      <c r="L71" t="n">
+        <v>122387.74</v>
+      </c>
+      <c r="M71" t="n">
+        <v>1774.1</v>
+      </c>
+      <c r="N71" t="n">
+        <v>48868.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N71"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3848,6 +3848,54 @@
         <v>48868.34</v>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>00:29:26</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>56199</v>
+      </c>
+      <c r="D72" t="n">
+        <v>1660.04</v>
+      </c>
+      <c r="E72" t="n">
+        <v>1499</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G72" t="n">
+        <v>55.27</v>
+      </c>
+      <c r="H72" t="n">
+        <v>128.65</v>
+      </c>
+      <c r="I72" t="n">
+        <v>129.65</v>
+      </c>
+      <c r="J72" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="K72" t="n">
+        <v>193.7</v>
+      </c>
+      <c r="L72" t="n">
+        <v>120702.63</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1761.08</v>
+      </c>
+      <c r="N72" t="n">
+        <v>48665.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:N73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3896,6 +3896,54 @@
         <v>48665.35</v>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>00:31:32</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>56410</v>
+      </c>
+      <c r="D73" t="n">
+        <v>1668.75</v>
+      </c>
+      <c r="E73" t="n">
+        <v>1499</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G73" t="n">
+        <v>55.27</v>
+      </c>
+      <c r="H73" t="n">
+        <v>128.65</v>
+      </c>
+      <c r="I73" t="n">
+        <v>129.65</v>
+      </c>
+      <c r="J73" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="K73" t="n">
+        <v>193.75</v>
+      </c>
+      <c r="L73" t="n">
+        <v>122354.87</v>
+      </c>
+      <c r="M73" t="n">
+        <v>1775.76</v>
+      </c>
+      <c r="N73" t="n">
+        <v>48899.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N73"/>
+  <dimension ref="A1:N74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3944,6 +3944,54 @@
         <v>48899.11</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>00:37:23</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>55357</v>
+      </c>
+      <c r="D74" t="n">
+        <v>1621.34</v>
+      </c>
+      <c r="E74" t="n">
+        <v>1499</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="G74" t="n">
+        <v>55.27</v>
+      </c>
+      <c r="H74" t="n">
+        <v>128.65</v>
+      </c>
+      <c r="I74" t="n">
+        <v>129.65</v>
+      </c>
+      <c r="J74" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="K74" t="n">
+        <v>188.42</v>
+      </c>
+      <c r="L74" t="n">
+        <v>123952.62</v>
+      </c>
+      <c r="M74" t="n">
+        <v>1835.73</v>
+      </c>
+      <c r="N74" t="n">
+        <v>49195.11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N74"/>
+  <dimension ref="A1:N75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3992,6 +3992,54 @@
         <v>49195.11</v>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>00:41:51</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>55136</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1630.18</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1513.8</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G75" t="n">
+        <v>55.28</v>
+      </c>
+      <c r="H75" t="n">
+        <v>128.75</v>
+      </c>
+      <c r="I75" t="n">
+        <v>129.79</v>
+      </c>
+      <c r="J75" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="K75" t="n">
+        <v>188.38</v>
+      </c>
+      <c r="L75" t="n">
+        <v>123523.8</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1810.95</v>
+      </c>
+      <c r="N75" t="n">
+        <v>48897.16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N75"/>
+  <dimension ref="A1:N76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4040,6 +4040,54 @@
         <v>48897.16</v>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>00:40:45</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>54946</v>
+      </c>
+      <c r="D76" t="n">
+        <v>1628.35</v>
+      </c>
+      <c r="E76" t="n">
+        <v>1554</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="G76" t="n">
+        <v>55.32</v>
+      </c>
+      <c r="H76" t="n">
+        <v>128.7</v>
+      </c>
+      <c r="I76" t="n">
+        <v>129.63</v>
+      </c>
+      <c r="J76" t="n">
+        <v>9.44</v>
+      </c>
+      <c r="K76" t="n">
+        <v>194.35</v>
+      </c>
+      <c r="L76" t="n">
+        <v>124330.7</v>
+      </c>
+      <c r="M76" t="n">
+        <v>1821.13</v>
+      </c>
+      <c r="N76" t="n">
+        <v>49026.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Prijzen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prijzen" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N76"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4088,6 +4088,54 @@
         <v>49026.25</v>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>00:41:28</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>55087</v>
+      </c>
+      <c r="D77" t="n">
+        <v>1638.1</v>
+      </c>
+      <c r="E77" t="n">
+        <v>1567</v>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="n">
+        <v>55.12</v>
+      </c>
+      <c r="H77" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="I77" t="n">
+        <v>129.61</v>
+      </c>
+      <c r="J77" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="K77" t="n">
+        <v>195.34</v>
+      </c>
+      <c r="L77" t="n">
+        <v>122997.1</v>
+      </c>
+      <c r="M77" t="n">
+        <v>1801.96</v>
+      </c>
+      <c r="N77" t="n">
+        <v>48028.1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N77"/>
+  <dimension ref="A1:N78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4136,6 +4136,54 @@
         <v>48028.1</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>00:22:46</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>54270</v>
+      </c>
+      <c r="D78" t="n">
+        <v>1621.61</v>
+      </c>
+      <c r="E78" t="n">
+        <v>1609.4</v>
+      </c>
+      <c r="F78" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="G78" t="n">
+        <v>55.12</v>
+      </c>
+      <c r="H78" t="n">
+        <v>128.8</v>
+      </c>
+      <c r="I78" t="n">
+        <v>129.61</v>
+      </c>
+      <c r="J78" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="K78" t="n">
+        <v>194.56</v>
+      </c>
+      <c r="L78" t="n">
+        <v>123127.42</v>
+      </c>
+      <c r="M78" t="n">
+        <v>1800.93</v>
+      </c>
+      <c r="N78" t="n">
+        <v>48806.47</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N78"/>
+  <dimension ref="A1:N79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4184,6 +4184,54 @@
         <v>48806.47</v>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>00:21:28</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>54524</v>
+      </c>
+      <c r="D79" t="n">
+        <v>1627.45</v>
+      </c>
+      <c r="E79" t="n">
+        <v>1579.6</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G79" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="H79" t="n">
+        <v>128.84</v>
+      </c>
+      <c r="I79" t="n">
+        <v>129.84</v>
+      </c>
+      <c r="J79" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="K79" t="n">
+        <v>194.56</v>
+      </c>
+      <c r="L79" t="n">
+        <v>121693.9</v>
+      </c>
+      <c r="M79" t="n">
+        <v>1805.46</v>
+      </c>
+      <c r="N79" t="n">
+        <v>48617.55</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N79"/>
+  <dimension ref="A1:N80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4232,6 +4232,54 @@
         <v>48617.55</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>00:20:36</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>54342</v>
+      </c>
+      <c r="D80" t="n">
+        <v>1621.36</v>
+      </c>
+      <c r="E80" t="n">
+        <v>1579.6</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G80" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="H80" t="n">
+        <v>128.84</v>
+      </c>
+      <c r="I80" t="n">
+        <v>129.84</v>
+      </c>
+      <c r="J80" t="n">
+        <v>9.470000000000001</v>
+      </c>
+      <c r="K80" t="n">
+        <v>194.58</v>
+      </c>
+      <c r="L80" t="n">
+        <v>123194.47</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1803.92</v>
+      </c>
+      <c r="N80" t="n">
+        <v>48837.12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N80"/>
+  <dimension ref="A1:N81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4280,6 +4280,54 @@
         <v>48837.12</v>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>00:24:33</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>55508</v>
+      </c>
+      <c r="D81" t="n">
+        <v>1643.83</v>
+      </c>
+      <c r="E81" t="n">
+        <v>1579.6</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G81" t="n">
+        <v>55.46</v>
+      </c>
+      <c r="H81" t="n">
+        <v>128.84</v>
+      </c>
+      <c r="I81" t="n">
+        <v>129.84</v>
+      </c>
+      <c r="J81" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="K81" t="n">
+        <v>194.27</v>
+      </c>
+      <c r="L81" t="n">
+        <v>124165.81</v>
+      </c>
+      <c r="M81" t="n">
+        <v>1829.73</v>
+      </c>
+      <c r="N81" t="n">
+        <v>49455.35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N81"/>
+  <dimension ref="A1:N82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4328,6 +4328,54 @@
         <v>49455.35</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>00:23:42</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>55768</v>
+      </c>
+      <c r="D82" t="n">
+        <v>1653</v>
+      </c>
+      <c r="E82" t="n">
+        <v>1621.2</v>
+      </c>
+      <c r="F82" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G82" t="n">
+        <v>55.17</v>
+      </c>
+      <c r="H82" t="n">
+        <v>128.72</v>
+      </c>
+      <c r="I82" t="n">
+        <v>129.65</v>
+      </c>
+      <c r="J82" t="n">
+        <v>9.43</v>
+      </c>
+      <c r="K82" t="n">
+        <v>189.77</v>
+      </c>
+      <c r="L82" t="n">
+        <v>122023.31</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1762.69</v>
+      </c>
+      <c r="N82" t="n">
+        <v>47706.48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N82"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4376,6 +4376,54 @@
         <v>47706.48</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>00:24:39</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>59294</v>
+      </c>
+      <c r="D83" t="n">
+        <v>1939.75</v>
+      </c>
+      <c r="E83" t="n">
+        <v>1541.8</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G83" t="n">
+        <v>55.42</v>
+      </c>
+      <c r="H83" t="n">
+        <v>127.42</v>
+      </c>
+      <c r="I83" t="n">
+        <v>128.46</v>
+      </c>
+      <c r="J83" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="K83" t="n">
+        <v>186.23</v>
+      </c>
+      <c r="L83" t="n">
+        <v>125996.82</v>
+      </c>
+      <c r="M83" t="n">
+        <v>1847.62</v>
+      </c>
+      <c r="N83" t="n">
+        <v>50487.34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:N84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4424,6 +4424,54 @@
         <v>50487.34</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>00:27:37</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>62296</v>
+      </c>
+      <c r="D84" t="n">
+        <v>1981.7</v>
+      </c>
+      <c r="E84" t="n">
+        <v>1507.6</v>
+      </c>
+      <c r="F84" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="G84" t="n">
+        <v>55.36</v>
+      </c>
+      <c r="H84" t="n">
+        <v>126.99</v>
+      </c>
+      <c r="I84" t="n">
+        <v>128.03</v>
+      </c>
+      <c r="J84" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="K84" t="n">
+        <v>185.56</v>
+      </c>
+      <c r="L84" t="n">
+        <v>125878.39</v>
+      </c>
+      <c r="M84" t="n">
+        <v>1876.14</v>
+      </c>
+      <c r="N84" t="n">
+        <v>50714.51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N84"/>
+  <dimension ref="A1:N85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4472,6 +4472,54 @@
         <v>50714.51</v>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>00:25:07</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>67281</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2171.71</v>
+      </c>
+      <c r="E85" t="n">
+        <v>1505.4</v>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="n">
+        <v>55.29</v>
+      </c>
+      <c r="H85" t="n">
+        <v>126.18</v>
+      </c>
+      <c r="I85" t="n">
+        <v>127.07</v>
+      </c>
+      <c r="J85" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="K85" t="n">
+        <v>183.86</v>
+      </c>
+      <c r="L85" t="n">
+        <v>128337.05</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1899.89</v>
+      </c>
+      <c r="N85" t="n">
+        <v>52071.54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N85"/>
+  <dimension ref="A1:N86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4520,6 +4520,54 @@
         <v>52071.54</v>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>00:21:37</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>65976</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2070.55</v>
+      </c>
+      <c r="E86" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F86" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G86" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="H86" t="n">
+        <v>126.51</v>
+      </c>
+      <c r="I86" t="n">
+        <v>127.14</v>
+      </c>
+      <c r="J86" t="n">
+        <v>9.33</v>
+      </c>
+      <c r="K86" t="n">
+        <v>183.86</v>
+      </c>
+      <c r="L86" t="n">
+        <v>127304.65</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1912.45</v>
+      </c>
+      <c r="N86" t="n">
+        <v>51958.66</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N86"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4568,6 +4568,54 @@
         <v>51958.66</v>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>00:21:41</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>66518</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2108.02</v>
+      </c>
+      <c r="E87" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G87" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="H87" t="n">
+        <v>126.51</v>
+      </c>
+      <c r="I87" t="n">
+        <v>127.14</v>
+      </c>
+      <c r="J87" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="K87" t="n">
+        <v>183.8</v>
+      </c>
+      <c r="L87" t="n">
+        <v>128660.85</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1909.55</v>
+      </c>
+      <c r="N87" t="n">
+        <v>52069.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N87"/>
+  <dimension ref="A1:N88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4616,6 +4616,54 @@
         <v>52069.8</v>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>00:26:23</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>67576</v>
+      </c>
+      <c r="D88" t="n">
+        <v>2125.56</v>
+      </c>
+      <c r="E88" t="n">
+        <v>1506</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="G88" t="n">
+        <v>55.58</v>
+      </c>
+      <c r="H88" t="n">
+        <v>126.51</v>
+      </c>
+      <c r="I88" t="n">
+        <v>127.14</v>
+      </c>
+      <c r="J88" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="K88" t="n">
+        <v>178.67</v>
+      </c>
+      <c r="L88" t="n">
+        <v>129946.36</v>
+      </c>
+      <c r="M88" t="n">
+        <v>1902.13</v>
+      </c>
+      <c r="N88" t="n">
+        <v>52180.23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/prijzen.xlsx
+++ b/prijzen.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:N89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4664,6 +4664,54 @@
         <v>52180.23</v>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>00:27:20</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>67526</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2096.17</v>
+      </c>
+      <c r="E89" t="n">
+        <v>1489.8</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="G89" t="n">
+        <v>55.59</v>
+      </c>
+      <c r="H89" t="n">
+        <v>126.23</v>
+      </c>
+      <c r="I89" t="n">
+        <v>126.81</v>
+      </c>
+      <c r="J89" t="n">
+        <v>9.34</v>
+      </c>
+      <c r="K89" t="n">
+        <v>182.43</v>
+      </c>
+      <c r="L89" t="n">
+        <v>130032.94</v>
+      </c>
+      <c r="M89" t="n">
+        <v>1896.59</v>
+      </c>
+      <c r="N89" t="n">
+        <v>51509.91</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
